--- a/model_maker_web_v2/results/Sungrow/Sungrow_stage1.xlsx
+++ b/model_maker_web_v2/results/Sungrow/Sungrow_stage1.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Sungrow</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Communication Protocol of PV Grid-Connected String Inverters_V1.1.37_EN.pdf</t>
+          <t>Sungrow_StringInverter_Modbus_Protocol_v1137.pdf</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:58</t>
+          <t>2026-04-03 16:03</t>
         </is>
       </c>
     </row>
